--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output4.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Maintenance_Strategy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maintenance_Strategy" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Raw_Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Daily_EWMA_Fast</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Weekly_EWMA_Slow</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Signal_Gap</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deviation_Percent</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,7 +495,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -508,7 +520,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -533,7 +545,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,7 +570,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +595,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -608,7 +620,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -658,7 +670,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -683,7 +695,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -708,7 +720,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -783,7 +795,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -808,7 +820,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -833,7 +845,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -858,7 +870,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -883,7 +895,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -908,7 +920,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -933,7 +945,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -958,7 +970,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -983,7 +995,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1008,7 +1020,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1058,7 +1070,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1083,7 +1095,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1108,7 +1120,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1133,7 +1145,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1158,7 +1170,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1183,7 +1195,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1208,7 +1220,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1233,7 +1245,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1258,7 +1270,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1283,7 +1295,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1308,7 +1320,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1358,7 +1370,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1383,7 +1395,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1408,7 +1420,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1433,7 +1445,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1458,7 +1470,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1508,7 +1520,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1558,7 +1570,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1583,7 +1595,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -1633,7 +1645,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -1658,7 +1670,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1683,7 +1695,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1708,7 +1720,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1733,7 +1745,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1758,7 +1770,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -1783,7 +1795,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -1808,7 +1820,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -1833,7 +1845,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -1858,7 +1870,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -1883,7 +1895,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2008,7 +2020,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2058,7 +2070,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2083,7 +2095,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2133,7 +2145,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2158,7 +2170,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2183,7 +2195,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2258,7 +2270,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2283,7 +2295,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2308,7 +2320,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2383,7 +2395,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -2408,7 +2420,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -2433,7 +2445,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -2458,7 +2470,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -2483,7 +2495,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -2508,7 +2520,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -2533,7 +2545,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -2558,7 +2570,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -2583,7 +2595,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -2608,7 +2620,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -2633,7 +2645,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -2658,7 +2670,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -2683,7 +2695,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -2708,7 +2720,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -2733,7 +2745,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -2758,7 +2770,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -2783,7 +2795,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -2808,7 +2820,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -2833,7 +2845,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -2858,7 +2870,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -2883,7 +2895,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -2908,7 +2920,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -2958,7 +2970,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -2983,7 +2995,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -3008,7 +3020,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -3033,7 +3045,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3058,7 +3070,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -3108,7 +3120,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -3133,7 +3145,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -3158,7 +3170,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -3183,7 +3195,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -3208,7 +3220,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -3233,7 +3245,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -3258,7 +3270,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -3283,7 +3295,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -3358,7 +3370,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -3383,7 +3395,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -3433,7 +3445,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -3458,7 +3470,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -3483,7 +3495,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -3508,7 +3520,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -3533,7 +3545,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -3558,7 +3570,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -3583,7 +3595,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -3608,7 +3620,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -3683,7 +3695,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -3708,7 +3720,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -3758,7 +3770,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -3783,7 +3795,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -3833,7 +3845,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -3858,7 +3870,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -3883,7 +3895,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -3908,7 +3920,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -3933,7 +3945,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -3958,7 +3970,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -3983,7 +3995,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -4008,7 +4020,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -4033,7 +4045,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -4058,7 +4070,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -4083,7 +4095,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -4108,7 +4120,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -4158,7 +4170,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -4183,7 +4195,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -4208,7 +4220,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -4233,7 +4245,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -4283,7 +4295,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -4308,7 +4320,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -4333,7 +4345,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -4358,7 +4370,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -4408,7 +4420,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -4433,7 +4445,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -4458,7 +4470,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -4483,7 +4495,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -4508,7 +4520,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -4558,7 +4570,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -4608,7 +4620,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -4633,7 +4645,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -4658,7 +4670,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -4683,7 +4695,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -4708,7 +4720,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -4733,7 +4745,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -4758,7 +4770,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -4783,7 +4795,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -4808,7 +4820,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -4833,7 +4845,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -4883,7 +4895,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -4908,7 +4920,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -4933,7 +4945,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -4958,7 +4970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -4983,7 +4995,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -5008,7 +5020,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -5033,7 +5045,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -5058,7 +5070,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -5083,7 +5095,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -5133,7 +5145,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -5158,7 +5170,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -5183,7 +5195,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -5208,7 +5220,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -5233,7 +5245,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -5258,7 +5270,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -5283,7 +5295,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -5333,7 +5345,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -5358,7 +5370,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -5383,7 +5395,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -5408,7 +5420,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -5458,7 +5470,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -5483,7 +5495,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -5508,7 +5520,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -5533,7 +5545,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -5558,7 +5570,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -5583,7 +5595,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -5608,7 +5620,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -5633,7 +5645,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -5658,7 +5670,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -5683,7 +5695,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -5708,7 +5720,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -5733,7 +5745,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -5758,7 +5770,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -5783,7 +5795,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -5808,7 +5820,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -5858,7 +5870,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -5883,7 +5895,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -5908,7 +5920,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -5933,7 +5945,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -5958,7 +5970,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -5983,7 +5995,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -6008,7 +6020,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -6033,7 +6045,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -6058,7 +6070,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -6083,7 +6095,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -6108,7 +6120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -6133,7 +6145,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -6158,7 +6170,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -6183,7 +6195,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -6208,7 +6220,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -6233,7 +6245,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -6258,7 +6270,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -6283,7 +6295,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -6308,7 +6320,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -6333,7 +6345,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -6358,7 +6370,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -6383,7 +6395,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -6408,7 +6420,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -6433,7 +6445,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -6483,7 +6495,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -6508,7 +6520,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -6533,7 +6545,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -6583,7 +6595,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -6633,7 +6645,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -6658,7 +6670,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -6683,7 +6695,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -6733,7 +6745,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -6758,7 +6770,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -6808,7 +6820,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -6833,7 +6845,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -6858,7 +6870,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -6883,7 +6895,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -6908,7 +6920,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -6958,7 +6970,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -7008,7 +7020,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -7058,7 +7070,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -7083,7 +7095,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -7158,7 +7170,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -7183,7 +7195,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -7208,7 +7220,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -7233,7 +7245,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -7258,7 +7270,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -7308,7 +7320,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -7333,7 +7345,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -7358,7 +7370,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -7383,7 +7395,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -7408,7 +7420,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -7433,7 +7445,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -7458,7 +7470,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -7483,7 +7495,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -7508,7 +7520,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -7533,7 +7545,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -7558,7 +7570,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -7583,7 +7595,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -7608,7 +7620,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -7633,7 +7645,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -7658,7 +7670,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -7683,7 +7695,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -7708,7 +7720,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -7733,7 +7745,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -7758,7 +7770,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -7808,7 +7820,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -7833,7 +7845,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -7858,7 +7870,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -7883,7 +7895,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -7908,7 +7920,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -7933,7 +7945,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -7958,7 +7970,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -7983,7 +7995,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -8033,7 +8045,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -8058,7 +8070,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -8083,7 +8095,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -8108,7 +8120,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -8133,7 +8145,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -8158,7 +8170,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -8183,7 +8195,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -8208,7 +8220,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -8233,7 +8245,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -8258,7 +8270,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -8283,7 +8295,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -8308,7 +8320,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -8333,7 +8345,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -8358,7 +8370,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -8383,7 +8395,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -8408,7 +8420,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -8433,7 +8445,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -8458,7 +8470,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -8483,7 +8495,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -8508,7 +8520,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -8533,7 +8545,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -8558,7 +8570,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -8583,7 +8595,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -8608,7 +8620,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -8633,7 +8645,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -8658,7 +8670,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -8683,7 +8695,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -8708,7 +8720,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -8758,7 +8770,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -8783,7 +8795,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -8808,7 +8820,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -8833,7 +8845,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -8858,7 +8870,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -8883,7 +8895,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -8908,7 +8920,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -8933,7 +8945,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -8983,7 +8995,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -9008,7 +9020,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -9033,7 +9045,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -9058,7 +9070,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -9083,7 +9095,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -9108,7 +9120,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -9133,7 +9145,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -9158,7 +9170,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -9183,7 +9195,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -9208,7 +9220,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -9233,7 +9245,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -9258,7 +9270,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -9283,7 +9295,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -9308,7 +9320,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -9333,7 +9345,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -9358,7 +9370,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -9383,7 +9395,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -9408,7 +9420,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B360" t="inlineStr">
@@ -9433,7 +9445,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B361" t="inlineStr">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B362" t="inlineStr">
@@ -9483,7 +9495,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B363" t="inlineStr">
@@ -9508,7 +9520,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B364" t="inlineStr">
@@ -9533,7 +9545,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B365" t="inlineStr">
@@ -9558,7 +9570,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B366" t="inlineStr">
@@ -9583,7 +9595,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B367" t="inlineStr">
@@ -9608,7 +9620,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B368" t="inlineStr">
@@ -9633,7 +9645,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B369" t="inlineStr">
@@ -9658,7 +9670,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B370" t="inlineStr">
@@ -9683,7 +9695,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B371" t="inlineStr">
@@ -9708,7 +9720,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B372" t="inlineStr">
@@ -9733,7 +9745,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B373" t="inlineStr">
@@ -9758,7 +9770,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B374" t="inlineStr">
@@ -9783,7 +9795,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B375" t="inlineStr">
@@ -9808,7 +9820,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B376" t="inlineStr">
@@ -9833,7 +9845,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B377" t="inlineStr">
@@ -9858,7 +9870,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B378" t="inlineStr">
@@ -9883,7 +9895,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B379" t="inlineStr">
@@ -9908,7 +9920,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B380" t="inlineStr">
@@ -9933,7 +9945,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B381" t="inlineStr">
@@ -9958,7 +9970,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B382" t="inlineStr">
@@ -9983,7 +9995,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B383" t="inlineStr">
@@ -10008,7 +10020,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B384" t="inlineStr">
@@ -10033,7 +10045,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B385" t="inlineStr">
@@ -10058,7 +10070,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B386" t="inlineStr">
@@ -10083,7 +10095,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B387" t="inlineStr">
@@ -10108,7 +10120,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B388" t="inlineStr">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B389" t="inlineStr">
@@ -10158,7 +10170,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B390" t="inlineStr">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B391" t="inlineStr">
@@ -10208,7 +10220,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B392" t="inlineStr">
@@ -10233,7 +10245,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B393" t="inlineStr">
@@ -10258,7 +10270,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B394" t="inlineStr">
@@ -10283,7 +10295,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B395" t="inlineStr">
@@ -10308,7 +10320,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B396" t="inlineStr">
@@ -10333,7 +10345,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B397" t="inlineStr">
@@ -10358,7 +10370,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B398" t="inlineStr">
@@ -10383,7 +10395,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B399" t="inlineStr">
@@ -10408,7 +10420,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B400" t="inlineStr">
@@ -10433,7 +10445,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B401" t="inlineStr">
@@ -10458,7 +10470,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B402" t="inlineStr">
@@ -10483,7 +10495,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B403" t="inlineStr">
@@ -10508,7 +10520,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B404" t="inlineStr">
@@ -10533,7 +10545,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B405" t="inlineStr">
@@ -10558,7 +10570,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B406" t="inlineStr">
@@ -10583,7 +10595,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B407" t="inlineStr">
@@ -10608,7 +10620,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B408" t="inlineStr">
@@ -10633,7 +10645,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B409" t="inlineStr">
@@ -10658,7 +10670,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B410" t="inlineStr">
@@ -10683,7 +10695,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B411" t="inlineStr">
@@ -10708,7 +10720,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B412" t="inlineStr">
@@ -10733,7 +10745,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B413" t="inlineStr">
@@ -10758,7 +10770,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B414" t="inlineStr">
@@ -10783,7 +10795,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B415" t="inlineStr">
@@ -10808,7 +10820,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B416" t="inlineStr">
@@ -10833,7 +10845,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B417" t="inlineStr">
@@ -10858,7 +10870,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B418" t="inlineStr">
@@ -10883,7 +10895,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B419" t="inlineStr">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B420" t="inlineStr">
@@ -10933,7 +10945,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B421" t="inlineStr">
@@ -10958,7 +10970,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B422" t="inlineStr">
@@ -10983,7 +10995,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B423" t="inlineStr">
@@ -11008,7 +11020,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B424" t="inlineStr">
@@ -11033,7 +11045,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B425" t="inlineStr">
@@ -11058,7 +11070,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B426" t="inlineStr">
@@ -11083,7 +11095,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B427" t="inlineStr">
@@ -11108,7 +11120,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B428" t="inlineStr">
@@ -11133,7 +11145,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B429" t="inlineStr">
@@ -11158,7 +11170,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B430" t="inlineStr">
@@ -11183,7 +11195,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B431" t="inlineStr">
@@ -11208,7 +11220,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B432" t="inlineStr">
@@ -11233,7 +11245,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B433" t="inlineStr">
@@ -11258,7 +11270,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B434" t="inlineStr">
@@ -11283,7 +11295,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B435" t="inlineStr">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B436" t="inlineStr">
@@ -11333,7 +11345,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B437" t="inlineStr">
@@ -11358,7 +11370,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B438" t="inlineStr">
@@ -11383,7 +11395,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B439" t="inlineStr">
@@ -11408,7 +11420,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B440" t="inlineStr">
@@ -11433,7 +11445,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B441" t="inlineStr">
@@ -11458,7 +11470,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B442" t="inlineStr">
@@ -11483,7 +11495,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B443" t="inlineStr">
@@ -11508,7 +11520,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B444" t="inlineStr">
@@ -11533,7 +11545,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B445" t="inlineStr">
@@ -11558,7 +11570,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B446" t="inlineStr">
@@ -11583,7 +11595,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B447" t="inlineStr">
@@ -11608,7 +11620,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B448" t="inlineStr">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B449" t="inlineStr">
@@ -11658,7 +11670,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B450" t="inlineStr">
@@ -11683,7 +11695,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B451" t="inlineStr">
@@ -11708,7 +11720,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B452" t="inlineStr">
@@ -11733,7 +11745,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B453" t="inlineStr">
@@ -11758,7 +11770,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B454" t="inlineStr">
@@ -11783,7 +11795,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B455" t="inlineStr">
@@ -11808,7 +11820,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B456" t="inlineStr">
@@ -11833,7 +11845,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B457" t="inlineStr">
@@ -11858,7 +11870,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B458" t="inlineStr">
@@ -11883,7 +11895,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B459" t="inlineStr">
@@ -11908,7 +11920,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B460" t="inlineStr">
@@ -11933,7 +11945,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B461" t="inlineStr">
@@ -11958,7 +11970,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B462" t="inlineStr">
@@ -11983,7 +11995,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B463" t="inlineStr">
@@ -12008,7 +12020,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B464" t="inlineStr">
@@ -12033,7 +12045,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B465" t="inlineStr">
@@ -12058,7 +12070,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B466" t="inlineStr">
@@ -12083,7 +12095,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B467" t="inlineStr">
@@ -12108,7 +12120,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B468" t="inlineStr">
@@ -12133,7 +12145,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B469" t="inlineStr">
@@ -12158,7 +12170,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B470" t="inlineStr">
@@ -12183,7 +12195,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B471" t="inlineStr">
@@ -12208,7 +12220,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B472" t="inlineStr">
@@ -12233,7 +12245,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B473" t="inlineStr">
@@ -12258,7 +12270,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B474" t="inlineStr">
@@ -12283,7 +12295,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B475" t="inlineStr">
@@ -12308,7 +12320,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B476" t="inlineStr">
@@ -12333,7 +12345,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B477" t="inlineStr">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B478" t="inlineStr">
@@ -12383,7 +12395,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B479" t="inlineStr">
@@ -12408,7 +12420,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B480" t="inlineStr">
@@ -12433,7 +12445,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B481" t="inlineStr">
@@ -12458,7 +12470,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B482" t="inlineStr">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B483" t="inlineStr">
@@ -12508,7 +12520,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B484" t="inlineStr">
@@ -12533,7 +12545,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B485" t="inlineStr">
@@ -12558,7 +12570,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B486" t="inlineStr">
@@ -12583,7 +12595,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B487" t="inlineStr">
@@ -12608,7 +12620,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B488" t="inlineStr">
@@ -12633,7 +12645,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B489" t="inlineStr">
@@ -12658,7 +12670,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B490" t="inlineStr">
@@ -12683,7 +12695,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B491" t="inlineStr">
@@ -12708,7 +12720,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B492" t="inlineStr">
@@ -12733,7 +12745,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B493" t="inlineStr">
@@ -12758,7 +12770,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B494" t="inlineStr">
@@ -12783,7 +12795,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B495" t="inlineStr">
@@ -12808,7 +12820,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B496" t="inlineStr">
@@ -12833,7 +12845,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B497" t="inlineStr">
@@ -12858,7 +12870,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B498" t="inlineStr">
@@ -12883,7 +12895,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B499" t="inlineStr">
@@ -12908,7 +12920,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B500" t="inlineStr">
@@ -12933,7 +12945,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B501" t="inlineStr">
@@ -12958,7 +12970,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B502" t="inlineStr">
@@ -12983,7 +12995,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B503" t="inlineStr">
@@ -13008,7 +13020,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B504" t="inlineStr">
@@ -13033,7 +13045,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B505" t="inlineStr">
@@ -13058,7 +13070,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B506" t="inlineStr">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B507" t="inlineStr">
@@ -13108,7 +13120,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B508" t="inlineStr">
@@ -13133,7 +13145,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B509" t="inlineStr">
@@ -13158,7 +13170,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B510" t="inlineStr">
@@ -13183,7 +13195,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B511" t="inlineStr">
@@ -13208,7 +13220,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B512" t="inlineStr">
@@ -13233,7 +13245,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B513" t="inlineStr">
@@ -13258,7 +13270,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B514" t="inlineStr">
@@ -13283,7 +13295,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B515" t="inlineStr">
@@ -13308,7 +13320,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B516" t="inlineStr">
@@ -13333,7 +13345,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B517" t="inlineStr">
@@ -13358,7 +13370,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B518" t="inlineStr">
@@ -13383,7 +13395,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B519" t="inlineStr">
@@ -13408,7 +13420,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B520" t="inlineStr">
@@ -13433,7 +13445,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B521" t="inlineStr">
@@ -13458,7 +13470,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B522" t="inlineStr">
@@ -13483,7 +13495,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B523" t="inlineStr">
@@ -13508,7 +13520,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B524" t="inlineStr">
@@ -13533,7 +13545,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B525" t="inlineStr">
@@ -13558,7 +13570,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B526" t="inlineStr">
@@ -13583,7 +13595,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B527" t="inlineStr">
@@ -13608,7 +13620,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B528" t="inlineStr">
@@ -13633,7 +13645,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B529" t="inlineStr">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B530" t="inlineStr">
@@ -13683,7 +13695,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B531" t="inlineStr">
@@ -13708,7 +13720,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B532" t="inlineStr">
@@ -13733,7 +13745,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B533" t="inlineStr">
@@ -13758,7 +13770,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B534" t="inlineStr">
@@ -13783,7 +13795,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B535" t="inlineStr">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B536" t="inlineStr">
@@ -13833,7 +13845,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B537" t="inlineStr">
@@ -13858,7 +13870,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B538" t="inlineStr">
@@ -13883,7 +13895,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B539" t="inlineStr">
@@ -13908,7 +13920,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B540" t="inlineStr">
@@ -13933,7 +13945,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B541" t="inlineStr">
@@ -13958,7 +13970,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B542" t="inlineStr">
@@ -13983,7 +13995,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B543" t="inlineStr">
@@ -14008,7 +14020,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B544" t="inlineStr">
@@ -14033,7 +14045,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B545" t="inlineStr">
@@ -14058,7 +14070,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B546" t="inlineStr">
@@ -14083,7 +14095,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B547" t="inlineStr">
@@ -14108,7 +14120,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B548" t="inlineStr">
@@ -14133,7 +14145,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B549" t="inlineStr">
@@ -14158,7 +14170,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B550" t="inlineStr">
@@ -14183,7 +14195,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B551" t="inlineStr">
@@ -14208,7 +14220,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B552" t="inlineStr">
@@ -14233,7 +14245,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B553" t="inlineStr">
@@ -14258,7 +14270,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B554" t="inlineStr">
@@ -14283,7 +14295,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B555" t="inlineStr">
@@ -14308,7 +14320,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B556" t="inlineStr">
@@ -14333,7 +14345,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B557" t="inlineStr">
@@ -14358,7 +14370,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B558" t="inlineStr">
@@ -14383,7 +14395,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B559" t="inlineStr">
@@ -14408,7 +14420,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B560" t="inlineStr">
@@ -14433,7 +14445,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B561" t="inlineStr">
@@ -14458,7 +14470,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B562" t="inlineStr">
@@ -14483,7 +14495,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B563" t="inlineStr">
@@ -14508,7 +14520,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B564" t="inlineStr">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B565" t="inlineStr">
@@ -14558,7 +14570,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B566" t="inlineStr">
@@ -14583,7 +14595,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B567" t="inlineStr">
@@ -14608,7 +14620,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B568" t="inlineStr">
@@ -14633,7 +14645,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B569" t="inlineStr">
@@ -14658,7 +14670,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B570" t="inlineStr">
@@ -14683,7 +14695,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B571" t="inlineStr">
@@ -14708,7 +14720,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B572" t="inlineStr">
@@ -14733,7 +14745,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B573" t="inlineStr">
@@ -14758,7 +14770,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B574" t="inlineStr">
@@ -14783,7 +14795,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B575" t="inlineStr">
@@ -14808,7 +14820,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B576" t="inlineStr">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B577" t="inlineStr">
@@ -14858,7 +14870,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B578" t="inlineStr">
@@ -14883,7 +14895,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B579" t="inlineStr">
@@ -14908,7 +14920,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B580" t="inlineStr">
@@ -14933,7 +14945,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B581" t="inlineStr">
@@ -14958,7 +14970,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B582" t="inlineStr">
@@ -14983,7 +14995,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B583" t="inlineStr">
@@ -15008,7 +15020,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B584" t="inlineStr">
@@ -15033,7 +15045,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B585" t="inlineStr">
@@ -15058,7 +15070,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B586" t="inlineStr">
@@ -15083,7 +15095,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B587" t="inlineStr">
@@ -15108,7 +15120,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B588" t="inlineStr">
@@ -15133,7 +15145,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B589" t="inlineStr">
@@ -15158,7 +15170,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B590" t="inlineStr">
@@ -15183,7 +15195,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B591" t="inlineStr">
@@ -15208,7 +15220,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B592" t="inlineStr">
@@ -15233,7 +15245,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B593" t="inlineStr">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B594" t="inlineStr">
@@ -15283,7 +15295,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B595" t="inlineStr">
@@ -15308,7 +15320,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B596" t="inlineStr">
@@ -15333,7 +15345,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B597" t="inlineStr">
@@ -15358,7 +15370,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B598" t="inlineStr">
@@ -15383,7 +15395,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B599" t="inlineStr">
@@ -15408,7 +15420,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B600" t="inlineStr">
@@ -15433,7 +15445,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B601" t="inlineStr">
@@ -15458,7 +15470,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B602" t="inlineStr">
@@ -15483,7 +15495,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B603" t="inlineStr">
@@ -15508,7 +15520,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B604" t="inlineStr">
@@ -15533,7 +15545,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B605" t="inlineStr">
@@ -15558,7 +15570,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B606" t="inlineStr">
@@ -15583,7 +15595,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B607" t="inlineStr">
@@ -15608,7 +15620,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B608" t="inlineStr">
@@ -15633,7 +15645,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B609" t="inlineStr">
